--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항일람.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항일람.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8970"/>
   </bookViews>
   <sheets>
-    <sheet name="20260428_요구사항일람" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="20260428_요구사항일람" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
   <si>
     <t>● 요구사항 일람</t>
   </si>
@@ -59,6 +59,45 @@
   </si>
   <si>
     <t>비회원의 임시 데이터(장바구니 등)는 서버 실행 시 또는 일정 주기로 자동 정리되어야 한다.</t>
+  </si>
+  <si>
+    <t>FR-11</t>
+  </si>
+  <si>
+    <t>쿠폰 발급 수량 제어</t>
+  </si>
+  <si>
+    <t>관리자가 쿠폰별 총 발급 수량을 동적으로 설정 가능</t>
+  </si>
+  <si>
+    <t>구현완료</t>
+  </si>
+  <si>
+    <t>FR-12</t>
+  </si>
+  <si>
+    <t>쿠폰 발급 대상 확장</t>
+  </si>
+  <si>
+    <t>리뷰 작성자 타겟팅 발급 기능</t>
+  </si>
+  <si>
+    <t>FR-13</t>
+  </si>
+  <si>
+    <t>프로모션 코드 연동</t>
+  </si>
+  <si>
+    <t>쿠폰별 고유 영문 코드 매핑</t>
+  </si>
+  <si>
+    <t>FR-14</t>
+  </si>
+  <si>
+    <t>자동 회원 등급제</t>
+  </si>
+  <si>
+    <t>구매 금액별 등급 자동 승급 로직</t>
   </si>
 </sst>
 </file>
@@ -67,32 +106,32 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="14"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="8"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -117,18 +156,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -137,21 +168,21 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -429,133 +460,244 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:F15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
+    <row r="1" ht="20.25" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="2">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="2">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="3">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="2">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="2">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="2">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="3">
         <v>5</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="2">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="3">
         <v>6</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="2">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="3">
         <v>7</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="2">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
         <v>8</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="2">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="3">
         <v>9</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="2">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="3">
         <v>10</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="2">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="3">
         <v>11</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="2">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="3">
         <v>12</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항일람.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항일람.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8970"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="20260428_요구사항일람" state="visible" r:id="rId4"/>
+    <sheet name="20260428_요구사항일람" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>● 요구사항 일람</t>
   </si>
@@ -61,43 +61,20 @@
     <t>비회원의 임시 데이터(장바구니 등)는 서버 실행 시 또는 일정 주기로 자동 정리되어야 한다.</t>
   </si>
   <si>
-    <t>FR-11</t>
-  </si>
-  <si>
-    <t>쿠폰 발급 수량 제어</t>
-  </si>
-  <si>
-    <t>관리자가 쿠폰별 총 발급 수량을 동적으로 설정 가능</t>
-  </si>
-  <si>
-    <t>구현완료</t>
-  </si>
-  <si>
-    <t>FR-12</t>
-  </si>
-  <si>
-    <t>쿠폰 발급 대상 확장</t>
-  </si>
-  <si>
-    <t>리뷰 작성자 타겟팅 발급 기능</t>
-  </si>
-  <si>
-    <t>FR-13</t>
-  </si>
-  <si>
-    <t>프로모션 코드 연동</t>
-  </si>
-  <si>
-    <t>쿠폰별 고유 영문 코드 매핑</t>
-  </si>
-  <si>
-    <t>FR-14</t>
-  </si>
-  <si>
-    <t>자동 회원 등급제</t>
-  </si>
-  <si>
-    <t>구매 금액별 등급 자동 승급 로직</t>
+    <t>관리자는 쿠폰별 총 발급 수량을 동적으로 설정할 수 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠폰 발급 대상으로 '리뷰 작성자'를 선택하여 타겟팅 발급이 가능하다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠폰 생성 및 수정 시 고유한 프로모션 코드를 매핑할 수 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원의 누적 구매 금액에 따라 등급(BRONZE/SILVER/GOLD/DIA)이 자동 갱신된다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -106,32 +83,32 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="14"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <color theme="1"/>
-      <family val="2"/>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
     </font>
   </fonts>
   <fills count="3">
@@ -156,33 +133,47 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -460,236 +451,156 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <dimension ref="B1:F19"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="2:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
         <v>5</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
         <v>6</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
         <v>8</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
         <v>9</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
         <v>10</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
         <v>11</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
         <v>12</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="5">
+        <v>13</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="5">
+        <v>14</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="5">
+        <v>15</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="5">
         <v>16</v>
       </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C19" s="6" t="s">
         <v>18</v>
       </c>
     </row>
@@ -697,7 +608,8 @@
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항일람.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항일람.xlsx
@@ -162,14 +162,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,13 +460,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
@@ -573,34 +573,34 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>13</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>14</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>15</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>16</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>18</v>
       </c>
     </row>
